--- a/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/StructureDefinition-at-elga-ediag-condition.xlsx
+++ b/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/StructureDefinition-at-elga-ediag-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T06:56:37+00:00</t>
+    <t>2026-09-09T15:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -527,7 +527,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose in einem internem Dokumentationssystem</t>
+    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem.</t>
   </si>
   <si>
     <t>Business identifiers assigned to this condition by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -555,8 +555,7 @@
 </t>
   </si>
   <si>
-    <t>Klinischer Status der Diagnose (wie:Status post), 
-mögliche Codes: active | recurrence | relapse | inactive | remission | resolved</t>
+    <t>Klinischer Status der Diagnose (z. B. Status post); mögliche Codes: active | recurrence | relapse | inactive | remission | resolved.</t>
   </si>
   <si>
     <t>The clinical status of the condition.</t>
@@ -597,7 +596,7 @@
     <t>Condition.verificationStatus</t>
   </si>
   <si>
-    <t>Status der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error</t>
+    <t>Verifizierungsstatus der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error.</t>
   </si>
   <si>
     <t>The verification status to support the clinical status of the condition.</t>
@@ -663,7 +662,7 @@
     <t>Condition.severity</t>
   </si>
   <si>
-    <t>Schweregrad der Erkrankung</t>
+    <t>Schweregrad der Erkrankung.</t>
   </si>
   <si>
     <t>A subjective assessment of the severity of the condition as evaluated by the clinician.</t>
@@ -697,7 +696,7 @@
 </t>
   </si>
   <si>
-    <t>Diagnosecode (Codierservice), Text verboten, Codesystem 1.SNOMED 2.Orphanet</t>
+    <t>Diagnosecode (Codierservice); Freitext ist nicht zulässig. Codesysteme: 1. SNOMED CT, 2. Orphanet.</t>
   </si>
   <si>
     <t>Identification of the condition, problem or diagnosis.</t>
@@ -1022,7 +1021,7 @@
     <t>Condition.bodySite</t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose der Körper-Lokalisation</t>
+    <t>Zuordnung der Diagnose zu einer Körperstelle.</t>
   </si>
   <si>
     <t>The anatomical location where this condition manifests itself.</t>
@@ -1057,7 +1056,7 @@
 </t>
   </si>
   <si>
-    <t>Person, auf die sich die Diagnose bezieht</t>
+    <t>Person, auf die sich die Diagnose bezieht.</t>
   </si>
   <si>
     <t>Indicates the patient or group who the condition record is associated with.</t>
@@ -1085,7 +1084,7 @@
 </t>
   </si>
   <si>
-    <t>Behandlungskontakt</t>
+    <t>Behandlungskontakt.</t>
   </si>
   <si>
     <t>The Encounter during which this Condition was created or to which the creation of this record is tightly associated.</t>
@@ -1113,7 +1112,7 @@
 </t>
   </si>
   <si>
-    <t>Beginn der Erkrankung/Diagnosezeitpunkt</t>
+    <t>Beginn der Erkrankung bzw. Diagnosezeitpunkt.</t>
   </si>
   <si>
     <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
@@ -1137,7 +1136,7 @@
     <t>Condition.abatement[x]</t>
   </si>
   <si>
-    <t>Ende der Erkrankung</t>
+    <t>Ende der Erkrankung.</t>
   </si>
   <si>
     <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
@@ -1159,7 +1158,7 @@
     <t>Condition.recordedDate</t>
   </si>
   <si>
-    <t>Zeitpunkt der Diagnosendokumentation</t>
+    <t>Zeitpunkt der Dokumentation der Diagnose.</t>
   </si>
   <si>
     <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
@@ -1181,7 +1180,7 @@
 </t>
   </si>
   <si>
-    <t>Ansonsten Gesundheitsdiensteanbieter, der die Diagnose eingetragen hat</t>
+    <t>GDA, der die Diagnose eingetragen hat.</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -1200,7 +1199,7 @@
 </t>
   </si>
   <si>
-    <t>Quelle der Information zur Diagnose (z. B. behandelnde Person, Patient oder Dritter)</t>
+    <t>Quelle der Information zur Diagnose (z. B. behandelnde GDA, Patient oder Dritter).</t>
   </si>
   <si>
     <t>Individual who is making the condition statement.</t>
@@ -1222,7 +1221,7 @@
 </t>
   </si>
   <si>
-    <t>Stadium der Erkrankung</t>
+    <t>Stadium der Erkrankung.</t>
   </si>
   <si>
     <t>Clinical stage or grade of a condition. May include formal severity assessments.</t>
@@ -1317,7 +1316,7 @@
     <t>Condition.evidence</t>
   </si>
   <si>
-    <t>Verweis auf ELGA-Befunde als medizinische Evidenz</t>
+    <t>Verweis auf ELGA-Befunde als medizinische Evidenz.</t>
   </si>
   <si>
     <t>Supporting evidence / manifestations that are the basis of the Condition's verification status, such as evidence that confirmed or refuted the condition.</t>
@@ -1390,7 +1389,7 @@
 </t>
   </si>
   <si>
-    <t>Freitext zur Diagnose für Zusatzinformation</t>
+    <t>Freitext zur Diagnose als Zusatzinformation.</t>
   </si>
   <si>
     <t>Additional information about the Condition. This is a general notes/comments entry  for description of the Condition, its diagnosis and prognosis.</t>
